--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.17-authentication-information/WKBK/90_workbooks/ISMS-IMP-A.5.17.1_Authentication_Policy_and_Standards_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.17-authentication-information/WKBK/90_workbooks/ISMS-IMP-A.5.17.1_Authentication_Policy_and_Standards_20260208.xlsx
@@ -2986,7 +2986,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Password policy settings from AD/Azure AD</t>
+          <t>Password policy settings from AD/Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
